--- a/story/地理分布.xlsx
+++ b/story/地理分布.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="12800" windowHeight="12080"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -98,7 +98,7 @@
   </si>
   <si>
     <t>莎车、且末(父)
-鄯善、扜弥(母)</t>
+扜弥(母)</t>
   </si>
   <si>
     <t>昆仑山北麓
@@ -106,7 +106,7 @@
 于阗、精绝(母)</t>
   </si>
   <si>
-    <t>东女(女)</t>
+    <t>鄯善、东女(女)</t>
   </si>
   <si>
     <t>苏毗(女)、瑶池(母)</t>
@@ -867,7 +867,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -901,18 +901,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -920,9 +914,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1292,34 +1283,34 @@
       <c r="F3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="11"/>
+      <c r="G3" s="8"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
     <row r="4" customHeight="1" spans="1:9">
       <c r="A4" s="1"/>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="12" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="11"/>
+      <c r="G4" s="8"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
     <row r="5" customHeight="1" spans="1:9">
       <c r="A5" s="1"/>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="9" t="s">
         <v>14</v>
       </c>
       <c r="C5" s="8" t="s">
@@ -1327,10 +1318,10 @@
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="12"/>
+      <c r="G5" s="11"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
     </row>
@@ -1345,13 +1336,13 @@
       <c r="D6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="12" t="s">
         <v>20</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H6" s="1"/>
@@ -1359,18 +1350,18 @@
     </row>
     <row r="7" customHeight="1" spans="1:9">
       <c r="A7" s="1"/>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="20" t="s">
+      <c r="D7" s="11"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="18" t="s">
         <v>26</v>
       </c>
       <c r="H7" s="1"/>
